--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104564_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104564_W12.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9341</v>
+        <v>5.5143</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5905</v>
+        <v>4.4543</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3436</v>
+        <v>1.06</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3482</v>
+        <v>3.3478</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9381</v>
+        <v>1.9277</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4101</v>
+        <v>1.42</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8063</v>
+        <v>2.7867</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6943</v>
+        <v>2.675</v>
       </c>
       <c r="L2" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5419</v>
+        <v>0.5611</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2982</v>
+        <v>1.3083</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2683</v>
+        <v>0.8479</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9599</v>
+        <v>0.8545</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3085</v>
+        <v>-0.0066</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2223</v>
+        <v>3.2604</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3104</v>
+        <v>0.3847</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5327</v>
+        <v>2.8757</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5321</v>
+        <v>0.5401</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4414</v>
+        <v>0.4477</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0906</v>
+        <v>0.0924</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2071</v>
+        <v>-0.2238</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8832</v>
+        <v>0.8791</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.0903</v>
+        <v>-1.1029</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7392</v>
+        <v>0.7639</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1809</v>
+        <v>1.1953</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1342</v>
+        <v>-0.0929</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8861</v>
+        <v>-0.156</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.248</v>
+        <v>0.0631</v>
       </c>
       <c r="V3" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="W3" t="n">
-        <v>3.278</v>
+        <v>3.2684</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1556</v>
+        <v>1.2676</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4593</v>
+        <v>-1.0047</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6149</v>
+        <v>2.2723</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1771</v>
+        <v>1.1863</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9581</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1352</v>
+        <v>2.1455</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5792</v>
+        <v>0.5658</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6896</v>
+        <v>-0.7002</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5979</v>
+        <v>0.6204</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1639</v>
+        <v>0.2603</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6775</v>
+        <v>-0.2047</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8414</v>
+        <v>0.465</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. HLINASON</t>
+          <t>M. NORMANTAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4265</v>
+        <v>0.0451</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.4006</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4917</v>
+        <v>-0.3555</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1275</v>
+        <v>-0.7887999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5699</v>
+        <v>1.0165</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4424</v>
+        <v>-1.8053</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2941</v>
+        <v>0.3857</v>
       </c>
       <c r="K5" t="n">
-        <v>1.697</v>
+        <v>1.965</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5971</v>
+        <v>-1.5793</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1666</v>
+        <v>-1.1745</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1272</v>
+        <v>-0.9485</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0395</v>
+        <v>-0.226</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7903</v>
+        <v>-0.3937</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1875</v>
+        <v>-0.5298</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9778</v>
+        <v>0.1361</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0965</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0965</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. NORMANTAS</t>
+          <t>T. HLINASON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5471</v>
+        <v>-0.3845</v>
       </c>
       <c r="E6" t="n">
-        <v>0.113</v>
+        <v>-0.4953</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6601</v>
+        <v>0.1107</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7943</v>
+        <v>1.1422</v>
       </c>
       <c r="H6" t="n">
-        <v>1.0129</v>
+        <v>1.5737</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.8072</v>
+        <v>-0.4315</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4014</v>
+        <v>2.285</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9741</v>
+        <v>1.6892</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.5727</v>
+        <v>0.5958</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1957</v>
+        <v>-1.1428</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.1155</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2345</v>
+        <v>-1.0273</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6805</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9796</v>
+        <v>-0.0196</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8347</v>
+        <v>-0.5903</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1449</v>
+        <v>0.5707</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>0.0863</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5463</v>
+        <v>0.0863</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6672</v>
+        <v>-1.0591</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5939</v>
+        <v>-2.3595</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9267</v>
+        <v>1.3004</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.418</v>
+        <v>-2.4028</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.746</v>
+        <v>-2.743</v>
       </c>
       <c r="I7" t="n">
-        <v>0.328</v>
+        <v>0.3402</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1232</v>
+        <v>-2.1338</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.2725</v>
+        <v>-2.2827</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2948</v>
+        <v>-0.269</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6167</v>
+        <v>0.2056</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7561</v>
+        <v>0.0019</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1394</v>
+        <v>0.2036</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7217</v>
+        <v>-1.5598</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.1757</v>
+        <v>-2.0142</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4539</v>
+        <v>0.4544</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4805</v>
+        <v>-1.4707</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2121</v>
+        <v>0.2152</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.6926</v>
+        <v>-1.686</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0262</v>
+        <v>-0.0397</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6856</v>
+        <v>0.6755</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.4543</v>
+        <v>-1.431</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9463</v>
+        <v>-0.7932</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9739</v>
+        <v>-0.7877</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0275</v>
+        <v>-0.0055</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.606</v>
+        <v>-1.7777</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.9338</v>
+        <v>-4.3311</v>
       </c>
       <c r="F9" t="n">
-        <v>2.3278</v>
+        <v>2.5535</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.4413</v>
+        <v>-2.4586</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.6651</v>
+        <v>-2.668</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2238</v>
+        <v>0.2094</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.5756</v>
+        <v>-2.6213</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.522</v>
+        <v>-2.538</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0536</v>
+        <v>-0.0832</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1343</v>
+        <v>0.1627</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2773</v>
+        <v>0.2926</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0967</v>
+        <v>-0.2508</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9557</v>
+        <v>-0.2954</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.141</v>
+        <v>0.0446</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8964</v>
+        <v>-2.5311</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8609</v>
+        <v>-3.7123</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9646</v>
+        <v>1.1812</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8656</v>
+        <v>-1.866</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6234</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2422</v>
+        <v>-1.2455</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0162</v>
+        <v>-1.0362</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1487</v>
+        <v>0.1411</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8494</v>
+        <v>-0.8298</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7721</v>
+        <v>-0.7617</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1481</v>
+        <v>-0.7758</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6956</v>
+        <v>-0.5089</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4525</v>
+        <v>-0.2669</v>
       </c>
       <c r="V10" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.6762</v>
+        <v>-8.4598</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.1322</v>
+        <v>-9.752599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4559</v>
+        <v>1.2928</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.1006</v>
+        <v>-4.1038</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5656</v>
+        <v>-1.5653</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5349</v>
+        <v>-2.5385</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.7657</v>
+        <v>-3.7898</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6203</v>
+        <v>-0.6313</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.1454</v>
+        <v>-3.1586</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3348</v>
+        <v>-0.3139</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1978</v>
+        <v>0.0373</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6956</v>
+        <v>-0.272</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4978</v>
+        <v>0.3093</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.376099999999999</v>
+        <v>-5.6846</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.8279</v>
+        <v>-18.4301</v>
       </c>
       <c r="F12" t="n">
-        <v>12.4517</v>
+        <v>12.7455</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.9154</v>
+        <v>-6.8743</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.383799999999999</v>
+        <v>-3.3752</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.5316</v>
+        <v>-3.4993</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.633</v>
+        <v>-3.8214</v>
       </c>
       <c r="K12" t="n">
-        <v>1.9785</v>
+        <v>1.8727</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.6114</v>
+        <v>-5.694</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.2823</v>
+        <v>-3.0529</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.362400000000001</v>
+        <v>-5.2479</v>
       </c>
       <c r="O12" t="n">
-        <v>2.08</v>
+        <v>2.1948</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="Q12" t="n">
-        <v>-21.5491</v>
+        <v>-21.6249</v>
       </c>
       <c r="R12" t="n">
-        <v>15.8783</v>
+        <v>15.9342</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6635</v>
+        <v>-0.9749000000000002</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.1906</v>
+        <v>-2.4884</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5272</v>
+        <v>1.5134</v>
       </c>
       <c r="V12" t="n">
-        <v>7.873600000000001</v>
+        <v>7.855400000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>9.544899999999998</v>
+        <v>9.5045</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6714</v>
+        <v>-1.6492</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.4773</v>
+        <v>7.1658</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1774</v>
+        <v>1.0118</v>
       </c>
       <c r="F13" t="n">
-        <v>6.2999</v>
+        <v>6.1539</v>
       </c>
       <c r="G13" t="n">
-        <v>4.1206</v>
+        <v>4.1109</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9108</v>
+        <v>1.8909</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2098</v>
+        <v>2.22</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9791</v>
+        <v>1.9429</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7552</v>
+        <v>1.7195</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M13" t="n">
-        <v>2.1415</v>
+        <v>2.168</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1556</v>
+        <v>0.1715</v>
       </c>
       <c r="O13" t="n">
-        <v>1.9859</v>
+        <v>1.9966</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R13" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7443</v>
+        <v>0.4403</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.1979</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8259</v>
+        <v>0.6382</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.1167</v>
+        <v>6.1459</v>
       </c>
       <c r="E14" t="n">
-        <v>4.915</v>
+        <v>4.7488</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2018</v>
+        <v>1.3971</v>
       </c>
       <c r="G14" t="n">
-        <v>8.381399999999999</v>
+        <v>8.3729</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2352</v>
+        <v>1.235</v>
       </c>
       <c r="I14" t="n">
-        <v>7.1462</v>
+        <v>7.1379</v>
       </c>
       <c r="J14" t="n">
-        <v>7.9567</v>
+        <v>7.9248</v>
       </c>
       <c r="K14" t="n">
-        <v>1.2051</v>
+        <v>1.1926</v>
       </c>
       <c r="L14" t="n">
-        <v>6.7516</v>
+        <v>6.7322</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4247</v>
+        <v>0.4481</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R14" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5066000000000001</v>
+        <v>0.547</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2662</v>
+        <v>0.1506</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2404</v>
+        <v>0.3964</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.8639</v>
+        <v>-1.8634</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="15">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8248</v>
+        <v>3.4961</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9747</v>
+        <v>-1.1101</v>
       </c>
       <c r="F15" t="n">
-        <v>4.7995</v>
+        <v>4.6062</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3498</v>
+        <v>2.3544</v>
       </c>
       <c r="H15" t="n">
-        <v>1.313</v>
+        <v>1.3207</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0369</v>
+        <v>1.0337</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5738</v>
+        <v>0.5603</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9524</v>
+        <v>0.948</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.3786</v>
+        <v>-0.3877</v>
       </c>
       <c r="M15" t="n">
-        <v>1.776</v>
+        <v>1.7941</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4154</v>
+        <v>1.4214</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>0.114</v>
+        <v>-0.2241</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1875</v>
+        <v>-0.3046</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3015</v>
+        <v>0.0805</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5797</v>
+        <v>2.4577</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4984</v>
+        <v>-1.0618</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0781</v>
+        <v>3.5195</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4063</v>
+        <v>1.4054</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4761</v>
+        <v>0.4822</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9302</v>
+        <v>0.9233</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2048</v>
+        <v>-0.2323</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4778</v>
+        <v>0.4686</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6825</v>
+        <v>-0.7009</v>
       </c>
       <c r="M16" t="n">
-        <v>1.6111</v>
+        <v>1.6377</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6127</v>
+        <v>1.6242</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0534</v>
+        <v>-0.1754</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7984</v>
+        <v>-0.3256</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.255</v>
+        <v>0.1503</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7405</v>
+        <v>0.4728</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.4978</v>
+        <v>-2.6331</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2382</v>
+        <v>3.1059</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3293</v>
+        <v>-0.3332</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8542</v>
+        <v>0.8558</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.1835</v>
+        <v>-1.189</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.153</v>
+        <v>-2.1705</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1314</v>
+        <v>0.1239</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M17" t="n">
-        <v>1.8237</v>
+        <v>1.8374</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7228</v>
+        <v>0.7319</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>0.121</v>
+        <v>-0.1533</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1179</v>
+        <v>-0.2349</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2389</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y. FALL</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3049</v>
+        <v>0.2137</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8202</v>
+        <v>-0.3438</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5153</v>
+        <v>0.5575</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.6015</v>
+        <v>0.3233</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3074</v>
+        <v>1.1232</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9089</v>
+        <v>-0.7999000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4512</v>
+        <v>0.7358</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3392</v>
+        <v>1.7269</v>
       </c>
       <c r="L18" t="n">
-        <v>0.112</v>
+        <v>-0.9912</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0526</v>
+        <v>-0.4125</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0318</v>
+        <v>-0.6037</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0209</v>
+        <v>0.1912</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2524</v>
+        <v>0.476</v>
       </c>
       <c r="T18" t="n">
-        <v>0.369</v>
+        <v>-0.2374</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8834</v>
+        <v>0.7134</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2534</v>
+        <v>-2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.387</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2534</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>Y. FALL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4931</v>
+        <v>-0.3825</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6654</v>
+        <v>0.4585</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1585</v>
+        <v>-0.8411</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5195</v>
+        <v>-0.6021</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5195</v>
+        <v>0.3019</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.904</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.4425</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.3308</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1117</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5195</v>
+        <v>-1.0446</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5195</v>
+        <v>-0.0289</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.0157</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6654</v>
+        <v>0.5563</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6654</v>
+        <v>0.0161</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.5402</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8642</v>
+        <v>-0.9563</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7865</v>
+        <v>0.195</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-1.1513</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3273</v>
+        <v>-0.5171</v>
       </c>
       <c r="H20" t="n">
-        <v>1.127</v>
+        <v>-0.5171</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7997</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7635</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7419</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9784</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4362</v>
+        <v>-0.5171</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6149</v>
+        <v>-0.5171</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1787</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0415</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.594</v>
+        <v>0.195</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7107</v>
+        <v>0.195</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1167</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3856</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.7997</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1005</v>
+        <v>-1.519</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7411</v>
+        <v>-2.4158</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6405</v>
+        <v>0.8968</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.836</v>
+        <v>-1.837</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9985</v>
+        <v>-1.9962</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1626</v>
+        <v>0.1592</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7389</v>
+        <v>-0.7639</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.88</v>
+        <v>-0.8898</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1411</v>
+        <v>0.1259</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0971</v>
+        <v>-1.0731</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1185</v>
+        <v>-1.1064</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0214</v>
+        <v>0.0333</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.07920000000000001</v>
+        <v>0.4969</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6412</v>
+        <v>-0.2861</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5619</v>
+        <v>0.7831</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4911</v>
+        <v>-4.7052</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3953</v>
+        <v>-4.7839</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0959</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2395</v>
+        <v>-1.2483</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4877</v>
+        <v>-0.4882</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7517</v>
+        <v>-0.7601</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0855</v>
+        <v>-1.1051</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.1649</v>
+        <v>-1.1773</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.154</v>
+        <v>-0.1432</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3342</v>
+        <v>0.1381</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3176</v>
+        <v>-0.0351</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0166</v>
+        <v>0.1732</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7189</v>
+        <v>-5.2177</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.1361</v>
+        <v>-6.8112</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4172</v>
+        <v>1.5935</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.1443</v>
+        <v>-5.1549</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.834</v>
+        <v>-0.833</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.3103</v>
+        <v>-4.3219</v>
       </c>
       <c r="J23" t="n">
-        <v>-4.2599</v>
+        <v>-4.2814</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.8198</v>
+        <v>-3.8365</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8844</v>
+        <v>-0.8734</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.394</v>
+        <v>-0.3881</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3478</v>
+        <v>0.1648</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>-0.2535</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2601</v>
+        <v>0.4182</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.376099999999999</v>
+        <v>7.171300000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-12.4519</v>
+        <v>-12.7456</v>
       </c>
       <c r="F24" t="n">
-        <v>18.8278</v>
+        <v>19.9167</v>
       </c>
       <c r="G24" t="n">
-        <v>6.915299999999999</v>
+        <v>6.874300000000002</v>
       </c>
       <c r="H24" t="n">
-        <v>3.384</v>
+        <v>3.3752</v>
       </c>
       <c r="I24" t="n">
-        <v>3.531600000000001</v>
+        <v>3.499200000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>3.282200000000001</v>
+        <v>3.053100000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>5.3625</v>
+        <v>5.247799999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.08</v>
+        <v>-2.194900000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>3.633200000000001</v>
+        <v>3.8214</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.9786</v>
+        <v>-1.8726</v>
       </c>
       <c r="O24" t="n">
-        <v>5.611499999999999</v>
+        <v>5.6941</v>
       </c>
       <c r="P24" t="n">
-        <v>5.6709</v>
+        <v>5.690900000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-15.8782</v>
+        <v>-15.9342</v>
       </c>
       <c r="R24" t="n">
-        <v>21.5491</v>
+        <v>21.6251</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6635</v>
+        <v>2.4616</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.527</v>
+        <v>-1.5134</v>
       </c>
       <c r="U24" t="n">
-        <v>3.1904</v>
+        <v>3.9751</v>
       </c>
       <c r="V24" t="n">
-        <v>-7.873699999999999</v>
+        <v>-7.8556</v>
       </c>
       <c r="W24" t="n">
-        <v>1.6714</v>
+        <v>1.6491</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.545000000000002</v>
+        <v>-9.504599999999998</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104564_W12.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104564_W12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-1.6492</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104564_W12.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-9.504599999999998</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
